--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/UTAH_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/UTAH_2018.xlsx
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C151">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C258">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C710">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C711">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C727">
